--- a/tests/results/results_tsmd.xlsx
+++ b/tests/results/results_tsmd.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bzcschae/workspace/scampi_paper/tests/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F8BDE3-3980-8D40-9BEB-27D1930E917C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770B057C-6A1F-1F44-A1D9-857187C3FB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13220" yWindow="780" windowWidth="28240" windowHeight="17240" xr2:uid="{E798825D-D367-6841-9413-660E20E17D01}"/>
+    <workbookView xWindow="-33480" yWindow="3460" windowWidth="28240" windowHeight="17240" xr2:uid="{E798825D-D367-6841-9413-660E20E17D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="107">
   <si>
     <t>dataset</t>
   </si>
@@ -342,12 +342,30 @@
   </si>
   <si>
     <t>0.4724 ± 0.1464</t>
+  </si>
+  <si>
+    <t>0.4115 ± 0.1121</t>
+  </si>
+  <si>
+    <t>0.4590 ± 0.0785</t>
+  </si>
+  <si>
+    <t>0.3187 ± 0.0571</t>
+  </si>
+  <si>
+    <t>0.2997 ± 0.0645</t>
+  </si>
+  <si>
+    <t>SCAMPI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -392,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -405,6 +423,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -739,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9086CCE7-C1FA-7D45-871C-9ABD9EF491FF}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="9.83203125" bestFit="1" customWidth="1"/>
@@ -923,6 +945,9 @@
       <c r="M4" t="s">
         <v>94</v>
       </c>
+      <c r="N4" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -964,6 +989,9 @@
       <c r="M5" t="s">
         <v>95</v>
       </c>
+      <c r="N5" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1005,6 +1033,9 @@
       <c r="M6" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="N6" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -1046,6 +1077,9 @@
       <c r="M7" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="N7" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1121,6 +1155,422 @@
       </c>
       <c r="L9" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.66</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I15" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J15" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="K15" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L15" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0.33139999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0.12</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0.33</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0.41</v>
+      </c>
+      <c r="I16" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0.51</v>
+      </c>
+      <c r="L16" s="7">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7">
+        <v>0.46810000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="7">
+        <v>0.63</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0.44</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0.46</v>
+      </c>
+      <c r="I17" s="7">
+        <v>0.66</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="K17" s="7">
+        <v>0.36</v>
+      </c>
+      <c r="L17" s="7">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7">
+        <v>0.39600000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0.53</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.38</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0.61</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0.68</v>
+      </c>
+      <c r="I18" s="7">
+        <v>0.54</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0.69</v>
+      </c>
+      <c r="K18" s="7">
+        <v>0.43</v>
+      </c>
+      <c r="L18" s="7">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7">
+        <v>0.4355</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="F19" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="G19" s="7">
+        <v>0.13</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="I19" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="J19" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="K19" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="L19" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0.34620000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="H20" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="I20" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="J20" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="K20" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="L20" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0.34150000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="7">
+        <v>0</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="7">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K21" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="L21" s="7">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="L22" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="M22" s="7"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B24" s="6">
+        <f>AVERAGE(B15:B20)</f>
+        <v>0.39666666666666667</v>
+      </c>
+      <c r="C24" s="6">
+        <f t="shared" ref="C24:M24" si="0">AVERAGE(C15:C20)</f>
+        <v>0.28833333333333333</v>
+      </c>
+      <c r="D24" s="6">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
+      </c>
+      <c r="E24" s="6">
+        <f t="shared" si="0"/>
+        <v>0.245</v>
+      </c>
+      <c r="F24" s="6">
+        <f t="shared" si="0"/>
+        <v>0.30166666666666664</v>
+      </c>
+      <c r="G24" s="6">
+        <f t="shared" si="0"/>
+        <v>0.29333333333333328</v>
+      </c>
+      <c r="H24" s="6">
+        <f t="shared" si="0"/>
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="0"/>
+        <v>0.33833333333333337</v>
+      </c>
+      <c r="J24" s="6">
+        <f t="shared" si="0"/>
+        <v>0.44333333333333336</v>
+      </c>
+      <c r="K24" s="6">
+        <f t="shared" si="0"/>
+        <v>0.32833333333333331</v>
+      </c>
+      <c r="L24" s="6">
+        <f t="shared" si="0"/>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="M24" s="6">
+        <f t="shared" si="0"/>
+        <v>0.38645000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/tests/results/results_tsmd.xlsx
+++ b/tests/results/results_tsmd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bzcschae/workspace/scampi_paper/tests/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770B057C-6A1F-1F44-A1D9-857187C3FB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F77A43-CA44-0D4F-8C71-33D297E403B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33480" yWindow="3460" windowWidth="28240" windowHeight="17240" xr2:uid="{E798825D-D367-6841-9413-660E20E17D01}"/>
+    <workbookView xWindow="17940" yWindow="3340" windowWidth="22360" windowHeight="21460" xr2:uid="{E798825D-D367-6841-9413-660E20E17D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="114">
   <si>
     <t>dataset</t>
   </si>
@@ -332,31 +332,54 @@
     <t>0.3415 ± 0.0659</t>
   </si>
   <si>
-    <t>SCAMPI + wlen</t>
-  </si>
-  <si>
-    <t>SCAMPI +min+max</t>
-  </si>
-  <si>
-    <t>0.3316 ± 0.0760</t>
-  </si>
-  <si>
-    <t>0.4724 ± 0.1464</t>
-  </si>
-  <si>
-    <t>0.4115 ± 0.1121</t>
-  </si>
-  <si>
-    <t>0.4590 ± 0.0785</t>
-  </si>
-  <si>
-    <t>0.3187 ± 0.0571</t>
-  </si>
-  <si>
-    <t>0.2997 ± 0.0645</t>
-  </si>
-  <si>
-    <t>SCAMPI</t>
+    <t>0.4761 ± 0.1358</t>
+  </si>
+  <si>
+    <t>0.7257 ± 0.1112</t>
+  </si>
+  <si>
+    <t>0.6079 ± 0.1033</t>
+  </si>
+  <si>
+    <t>0.3442 ± 0.0589</t>
+  </si>
+  <si>
+    <t>0.3348 ± 0.0669</t>
+  </si>
+  <si>
+    <t>0.2013 ± 0.0788</t>
+  </si>
+  <si>
+    <t>SCAMPI 
++min+max</t>
+  </si>
+  <si>
+    <t>SCAMPI
++slack</t>
+  </si>
+  <si>
+    <t>0.1524 ± 0.0385</t>
+  </si>
+  <si>
+    <t>k-Motiflets2</t>
+  </si>
+  <si>
+    <t>0.0728 ± 0.0386</t>
+  </si>
+  <si>
+    <t>0.4628 ± 0.1524</t>
+  </si>
+  <si>
+    <t>0.1480 ± 0.0778</t>
+  </si>
+  <si>
+    <t>0.1134 ± 0.0435</t>
+  </si>
+  <si>
+    <t>0.0731 ± 0.0137</t>
+  </si>
+  <si>
+    <t>0.1605 ± 0.0882</t>
   </si>
 </sst>
 </file>
@@ -366,7 +389,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -387,6 +410,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -410,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -424,9 +453,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -761,19 +796,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9086CCE7-C1FA-7D45-871C-9ABD9EF491FF}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -796,28 +831,32 @@
         <v>91</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N1" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="P1" s="13"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -840,28 +879,31 @@
         <v>17</v>
       </c>
       <c r="H2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="N2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -884,28 +926,31 @@
         <v>29</v>
       </c>
       <c r="H3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I3" t="s">
         <v>30</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>34</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>93</v>
       </c>
-      <c r="N3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -928,28 +973,31 @@
         <v>40</v>
       </c>
       <c r="H4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" t="s">
         <v>41</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>43</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>34</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>94</v>
       </c>
-      <c r="N4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
@@ -971,29 +1019,32 @@
       <c r="G5" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>51</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>53</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>54</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>95</v>
       </c>
-      <c r="N5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -1016,28 +1067,31 @@
         <v>61</v>
       </c>
       <c r="H6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I6" t="s">
         <v>62</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>63</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>64</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>65</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>66</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="N6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>67</v>
       </c>
@@ -1060,28 +1114,31 @@
         <v>73</v>
       </c>
       <c r="H7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" t="s">
         <v>74</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>75</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>76</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>77</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>78</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="N7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>79</v>
       </c>
@@ -1104,22 +1161,28 @@
         <v>81</v>
       </c>
       <c r="H8" t="s">
+        <v>113</v>
+      </c>
+      <c r="I8" t="s">
         <v>83</v>
       </c>
-      <c r="I8" t="s">
-        <v>81</v>
-      </c>
       <c r="J8" t="s">
         <v>81</v>
       </c>
       <c r="K8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" t="s">
         <v>84</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>85</v>
       </c>
@@ -1142,22 +1205,28 @@
         <v>81</v>
       </c>
       <c r="H9" t="s">
+        <v>112</v>
+      </c>
+      <c r="I9" t="s">
         <v>88</v>
       </c>
-      <c r="I9" t="s">
-        <v>81</v>
-      </c>
       <c r="J9" t="s">
         <v>81</v>
       </c>
       <c r="K9" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" t="s">
         <v>89</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>0</v>
       </c>
@@ -1180,356 +1249,409 @@
         <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="9">
         <v>0.25</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="9">
         <v>0.22</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="9">
         <v>0.17</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="9">
         <v>0.27</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="10">
         <v>0.66</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="9">
         <v>0.03</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15">
+        <v>7.2800000000000004E-2</v>
+      </c>
+      <c r="I15" s="9">
         <v>0.28999999999999998</v>
       </c>
-      <c r="I15" s="7">
+      <c r="J15" s="9">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J15" s="7">
+      <c r="K15" s="9">
         <v>0.2</v>
       </c>
-      <c r="K15" s="7">
+      <c r="L15" s="9">
         <v>0.28999999999999998</v>
       </c>
-      <c r="L15" s="7">
+      <c r="M15" s="9">
         <v>0.01</v>
       </c>
-      <c r="M15" s="9">
+      <c r="N15" s="8">
         <v>0.33139999999999997</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="6">
+        <v>0.33139999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="9">
         <v>0.5</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="9">
         <v>0.12</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="9">
         <v>0.28999999999999998</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="9">
         <v>0.33</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="9">
         <v>0.4</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16">
+        <v>0.46279999999999999</v>
+      </c>
+      <c r="I16" s="9">
         <v>0.41</v>
       </c>
-      <c r="I16" s="7">
+      <c r="J16" s="9">
         <v>0.17</v>
       </c>
-      <c r="J16" s="8">
+      <c r="K16" s="10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="K16" s="9">
+      <c r="L16" s="11">
         <v>0.51</v>
       </c>
-      <c r="L16" s="7">
+      <c r="M16" s="9">
         <v>0</v>
       </c>
-      <c r="M16" s="7">
+      <c r="N16" s="6">
         <v>0.46810000000000002</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O16" s="6">
+        <v>0.47610000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="9">
         <v>0.63</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="9">
         <v>0.69</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="9">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="9">
         <v>0.18</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="9">
         <v>0.44</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17">
+        <v>0.72570000000000001</v>
+      </c>
+      <c r="I17" s="9">
         <v>0.46</v>
       </c>
-      <c r="I17" s="7">
+      <c r="J17" s="9">
         <v>0.66</v>
       </c>
-      <c r="J17" s="8">
+      <c r="K17" s="10">
         <v>0.77</v>
       </c>
-      <c r="K17" s="7">
+      <c r="L17" s="9">
         <v>0.36</v>
       </c>
-      <c r="L17" s="7">
+      <c r="M17" s="9">
         <v>0</v>
       </c>
-      <c r="M17" s="7">
+      <c r="N17" s="6">
         <v>0.39600000000000002</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O17" s="6">
+        <v>0.72570000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="9">
         <v>0.49</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="11">
         <v>0.53</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="9">
         <v>0.38</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="9">
         <v>0.27</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="9">
         <v>0.18</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="9">
         <v>0.61</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18">
+        <v>0.6079</v>
+      </c>
+      <c r="I18" s="11">
         <v>0.68</v>
       </c>
-      <c r="I18" s="7">
+      <c r="J18" s="9">
         <v>0.54</v>
       </c>
-      <c r="J18" s="8">
+      <c r="K18" s="10">
         <v>0.69</v>
       </c>
-      <c r="K18" s="7">
+      <c r="L18" s="9">
         <v>0.43</v>
       </c>
-      <c r="L18" s="7">
+      <c r="M18" s="9">
         <v>0</v>
       </c>
-      <c r="M18" s="7">
+      <c r="N18" s="6">
         <v>0.4355</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O18" s="6">
+        <v>0.6079</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="9">
         <v>0.26</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="9">
         <v>0.1</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="10">
         <v>0.33</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="9">
         <v>0.26</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="9">
         <v>0.23</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="9">
         <v>0.13</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="I19" s="9">
         <v>0.18</v>
       </c>
-      <c r="I19" s="7">
+      <c r="J19" s="9">
         <v>0.17</v>
       </c>
-      <c r="J19" s="7">
+      <c r="K19" s="9">
         <v>0.23</v>
       </c>
-      <c r="K19" s="7">
+      <c r="L19" s="9">
         <v>0.2</v>
       </c>
-      <c r="L19" s="7">
+      <c r="M19" s="9">
         <v>0.1</v>
       </c>
-      <c r="M19" s="8">
+      <c r="N19" s="12">
         <v>0.34620000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O19" s="7">
+        <v>0.34420000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="9">
         <v>0.25</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="9">
         <v>0.05</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="10">
         <v>0.33</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="9">
         <v>0.24</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="9">
         <v>0.23</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="9">
         <v>0.15</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20">
+        <v>0.1134</v>
+      </c>
+      <c r="I20" s="9">
         <v>0.17</v>
       </c>
-      <c r="I20" s="7">
+      <c r="J20" s="9">
         <v>0.2</v>
       </c>
-      <c r="J20" s="7">
+      <c r="K20" s="9">
         <v>0.22</v>
       </c>
-      <c r="K20" s="7">
+      <c r="L20" s="9">
         <v>0.18</v>
       </c>
-      <c r="L20" s="7">
+      <c r="M20" s="9">
         <v>0.1</v>
       </c>
-      <c r="M20" s="8">
+      <c r="N20" s="12">
         <v>0.34150000000000003</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O20" s="7">
+        <v>0.33479999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="9">
         <v>0</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="7">
+      <c r="C21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="9">
         <v>0.03</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H21" s="7">
+      <c r="F21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0.1605</v>
+      </c>
+      <c r="I21" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="K21" s="7">
+      <c r="J21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="L21" s="9">
         <v>0.16</v>
       </c>
-      <c r="L21" s="7">
+      <c r="M21" s="9">
         <v>0</v>
       </c>
-      <c r="M21" s="7"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="9"/>
+      <c r="O21" s="7">
+        <v>0.20130000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="9">
         <v>0.06</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="7">
+      <c r="C22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H22" s="7">
+      <c r="F22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="9">
+        <v>7.3099999999999998E-2</v>
+      </c>
+      <c r="I22" s="9">
         <v>0.17</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="K22" s="7">
+      <c r="J22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="L22" s="9">
         <v>0.2</v>
       </c>
-      <c r="L22" s="7">
+      <c r="M22" s="9">
         <v>0.1</v>
       </c>
-      <c r="M22" s="7"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="9"/>
+      <c r="O22" s="12">
+        <v>0.15240000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B24" s="6">
         <f>AVERAGE(B15:B20)</f>
         <v>0.39666666666666667</v>
       </c>
       <c r="C24" s="6">
-        <f t="shared" ref="C24:M24" si="0">AVERAGE(C15:C20)</f>
+        <f t="shared" ref="C24:O25" si="0">AVERAGE(C15:C20)</f>
         <v>0.28833333333333333</v>
       </c>
       <c r="D24" s="6">
@@ -1550,27 +1672,65 @@
       </c>
       <c r="H24" s="6">
         <f t="shared" si="0"/>
-        <v>0.36499999999999999</v>
+        <v>0.35509999999999997</v>
       </c>
       <c r="I24" s="6">
         <f t="shared" si="0"/>
-        <v>0.33833333333333337</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="J24" s="6">
         <f t="shared" si="0"/>
-        <v>0.44333333333333336</v>
+        <v>0.33833333333333337</v>
       </c>
       <c r="K24" s="6">
         <f t="shared" si="0"/>
-        <v>0.32833333333333331</v>
+        <v>0.44333333333333336</v>
       </c>
       <c r="L24" s="6">
         <f t="shared" si="0"/>
-        <v>3.5000000000000003E-2</v>
+        <v>0.32833333333333331</v>
       </c>
       <c r="M24" s="6">
         <f t="shared" si="0"/>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="N24" s="6">
+        <f t="shared" si="0"/>
         <v>0.38645000000000002</v>
+      </c>
+      <c r="O24" s="7">
+        <f t="shared" si="0"/>
+        <v>0.47001666666666658</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B25" s="6">
+        <f>AVERAGE(B15:B22)</f>
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="E25" s="6">
+        <f>AVERAGE(E15:E22)</f>
+        <v>0.20500000000000002</v>
+      </c>
+      <c r="H25" s="6">
+        <f>AVERAGE(H15:H22)</f>
+        <v>0.29552499999999998</v>
+      </c>
+      <c r="I25" s="6">
+        <f>AVERAGE(I15:I22)</f>
+        <v>0.3125</v>
+      </c>
+      <c r="L25" s="6">
+        <f>AVERAGE(L15:L22)</f>
+        <v>0.29125000000000001</v>
+      </c>
+      <c r="M25" s="6">
+        <f>AVERAGE(M15:M22)</f>
+        <v>3.8750000000000007E-2</v>
+      </c>
+      <c r="O25" s="7">
+        <f>AVERAGE(O15:O22)</f>
+        <v>0.39672499999999994</v>
       </c>
     </row>
   </sheetData>
